--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -420,7 +420,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -440,7 +440,7 @@
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1988" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1988" uniqueCount="416">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -634,6 +634,11 @@
     <t>FR Core Organization Short Name Extension</t>
   </si>
   <si>
+    <t>Libellé court de l'organisation
++The Organization short name</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
@@ -651,6 +656,10 @@
     <t>FR Core Organization Description Extension</t>
   </si>
   <si>
+    <t>Description textuelle d'une organisation
+Organization description</t>
+  </si>
+  <si>
     <t>Organization.extension:budgetLetter</t>
   </si>
   <si>
@@ -664,7 +673,8 @@
     <t>FR Core Organization Budget Letter Extension</t>
   </si>
   <si>
-    <t>An organization budget letter | Lettre budgétaire de l'UF</t>
+    <t>Lettre budgétaire de l'UF
+An organization budget letter</t>
   </si>
   <si>
     <t>Organization.extension:usePeriod</t>
@@ -3750,7 +3760,7 @@
         <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3810,7 +3820,7 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>116</v>
@@ -3830,13 +3840,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>191</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>77</v>
@@ -3858,13 +3868,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3924,7 +3934,7 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>116</v>
@@ -3944,13 +3954,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>191</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>77</v>
@@ -3972,13 +3982,13 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4038,7 +4048,7 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>116</v>
@@ -4058,13 +4068,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>191</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>77</v>
@@ -4086,13 +4096,13 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>192</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4172,10 +4182,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4201,16 +4211,16 @@
         <v>108</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4259,7 +4269,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4288,10 +4298,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4314,17 +4324,17 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4373,7 +4383,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4382,30 +4392,30 @@
         <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4514,10 +4524,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4628,10 +4638,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4657,16 +4667,16 @@
         <v>167</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4691,11 +4701,11 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4713,7 +4723,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4731,7 +4741,7 @@
         <v>190</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4742,10 +4752,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4768,19 +4778,19 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4809,7 +4819,7 @@
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4827,7 +4837,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4842,10 +4852,10 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4856,10 +4866,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4885,16 +4895,16 @@
         <v>129</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4907,7 +4917,7 @@
         <v>77</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>77</v>
@@ -4943,7 +4953,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4958,13 +4968,13 @@
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -4972,10 +4982,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5001,13 +5011,13 @@
         <v>101</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5021,7 +5031,7 @@
         <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>77</v>
@@ -5057,7 +5067,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5072,13 +5082,13 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5086,10 +5096,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5112,13 +5122,13 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5169,7 +5179,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5184,13 +5194,13 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5198,10 +5208,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5224,16 +5234,16 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5283,7 +5293,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5298,13 +5308,13 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5312,10 +5322,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5338,70 +5348,70 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="P33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q33" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="R33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="P33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q33" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="R33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5416,24 +5426,24 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5456,19 +5466,19 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5497,7 +5507,7 @@
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5515,7 +5525,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5530,24 +5540,24 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5573,16 +5583,16 @@
         <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5631,7 +5641,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5640,19 +5650,19 @@
         <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5660,10 +5670,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5689,16 +5699,16 @@
         <v>101</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5747,7 +5757,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5765,7 +5775,7 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5776,10 +5786,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5802,19 +5812,19 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5863,7 +5873,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5872,19 +5882,19 @@
         <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -5892,10 +5902,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5918,19 +5928,19 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -5979,7 +5989,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5988,19 +5998,19 @@
         <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6008,10 +6018,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6034,17 +6044,17 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6093,7 +6103,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6108,10 +6118,10 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>105</v>
@@ -6122,10 +6132,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6234,10 +6244,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6348,10 +6358,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6377,13 +6387,13 @@
         <v>101</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6433,7 +6443,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6442,7 +6452,7 @@
         <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>99</v>
@@ -6462,10 +6472,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6491,13 +6501,13 @@
         <v>129</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6527,7 +6537,7 @@
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6545,7 +6555,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6574,10 +6584,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6600,16 +6610,16 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6659,7 +6669,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6677,7 +6687,7 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6688,10 +6698,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6717,13 +6727,13 @@
         <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6773,7 +6783,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6802,10 +6812,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6828,19 +6838,19 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6889,7 +6899,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6907,7 +6917,7 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6918,10 +6928,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7030,10 +7040,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7144,14 +7154,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7173,16 +7183,16 @@
         <v>108</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7231,7 +7241,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7260,10 +7270,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7286,17 +7296,17 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7324,10 +7334,10 @@
         <v>149</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -7345,7 +7355,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7363,7 +7373,7 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7374,10 +7384,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7400,17 +7410,17 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -7459,7 +7469,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7474,10 +7484,10 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7488,10 +7498,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7514,17 +7524,17 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7573,7 +7583,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7588,10 +7598,10 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -7602,10 +7612,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7628,17 +7638,17 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7687,7 +7697,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7702,10 +7712,10 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -7716,10 +7726,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7742,17 +7752,17 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7801,7 +7811,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:27:17+00:00</t>
+    <t>2025-05-20T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -683,7 +683,7 @@
     <t>usePeriod</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {organization-period}
+    <t xml:space="preserve">Extension {organization-period|5.2.0}
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -683,7 +683,7 @@
     <t>usePeriod</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {organization-period|5.2.0}
+    <t xml:space="preserve">Extension {organization-period|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -4162,7 +4162,7 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>116</v>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-pole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
